--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-ballot</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:44:45+00:00</t>
+    <t>2024-03-25T10:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:59:40+00:00</t>
+    <t>2024-03-25T11:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T08:02:06+00:00</t>
+    <t>2024-05-23T12:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:05:52+00:00</t>
+    <t>2024-05-23T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:32:02+00:00</t>
+    <t>2024-05-23T14:35:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T14:35:00+00:00</t>
+    <t>2024-06-11T15:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -13570,7 +13570,7 @@
         <v>83</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>258</v>
+        <v>158</v>
       </c>
       <c r="Y92" t="s" s="2">
         <v>667</v>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:12+00:00</t>
+    <t>2024-06-11T15:33:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:34+00:00</t>
+    <t>2024-07-02T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(WORK))</t>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T11:39:28+00:00</t>
+    <t>2024-07-17T12:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:13:27+00:00</t>
+    <t>2024-07-17T14:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T14:21:13+00:00</t>
+    <t>2024-07-17T15:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:15:49+00:00</t>
+    <t>2024-07-17T15:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T07:11:02+00:00</t>
+    <t>2024-07-25T15:28:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:28:42+00:00</t>
+    <t>2024-07-25T15:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:29:18+00:00</t>
+    <t>2024-07-25T15:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:44:10+00:00</t>
+    <t>2024-08-01T13:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0-ballot</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-03T15:38:30+00:00</t>
+    <t>2024-09-04T07:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T07:28:39+00:00</t>
+    <t>2024-09-04T07:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T12:53:53+00:00</t>
+    <t>2024-10-28T08:07:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -446,7 +446,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -466,7 +466,7 @@
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:07:18+00:00</t>
+    <t>2024-10-28T08:08:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profile of the ObservationResprate profil (described in the HL7 VitalSigns profil) for France.
+    <t>French profile for the ObservationResprate profil (described in the HL7 VitalSigns profil) for France.
 Profilage du profil ObservationResprate (décrit dans le profil HL7 VitaSigns) pour l'usage en France</t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:08:30+00:00</t>
+    <t>2024-10-29T10:42:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:05:50+00:00</t>
+    <t>2025-01-28T09:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:07:36+00:00</t>
+    <t>2025-02-04T08:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T08:51:44+00:00</t>
+    <t>2025-02-04T09:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:30:35+00:00</t>
+    <t>2025-02-19T13:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:47:59+00:00</t>
+    <t>2025-02-19T13:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:52:01+00:00</t>
+    <t>2025-02-19T13:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:53:58+00:00</t>
+    <t>2025-02-19T13:58:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -660,7 +660,8 @@
     <t>FR Core Observation Body Position Ext Extension</t>
   </si>
   <si>
-    <t>CIMI extension (in FHIR R4) defined in the context of the Respiratory Rate profile. This extension is used to specify the body position during the respiratory rate observation | Extension CIMI (upgardée en FHIR R4) définie dans le contexte du profil Respiratory rate. Cette extension permet de préciser la position du corps lors de la mesure de la fréquence respiratoire.</t>
+    <t>Extension CIMI (upgardée en FHIR R4) définie dans le contexte du profil Respiratory rate. Cette extension permet de préciser la position du corps lors de la mesure de la fréquence respiratoire.
+CIMI extension (in FHIR R4) defined in the context of the Respiratory Rate profile. This extension is used to specify the body position during the respiratory rate observation</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -680,7 +681,8 @@
     <t>FR Core Observation Level Of Exertion Extension</t>
   </si>
   <si>
-    <t>French extension defined in the context of the Vital Signs Resprate profile. This extension is used to define the level of exertion ( at rest, during exertion, post exertion) during the respiratory rate measure | Extension française définie dans le contexte du profil Vital Signs Resprate. Cette extension permet de préciser le niveau d'exercice du patient durant la mesure de la fréquence respiratoire (au repos, pendant l'effort, après l'effort)</t>
+    <t>Extension française définie dans le contexte du profil Vital Signs Resprate. Cette extension permet de préciser le niveau d'exercice du patient durant la mesure de la fréquence respiratoire (au repos, pendant l'effort, après l'effort).
+French extension defined in the context of the Vital Signs Resprate profile. This extension is used to define the level of exertion ( at rest, during exertion, post exertion) during the respiratory rate measure</t>
   </si>
   <si>
     <t>Observation.extension:supportingInfo</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:58:46+00:00</t>
+    <t>2025-02-19T14:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T14:07:54+00:00</t>
+    <t>2025-02-19T14:26:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:11:18+00:00</t>
+    <t>2025-05-20T13:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:27:17+00:00</t>
+    <t>2025-05-20T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:29:42+00:00</t>
+    <t>2025-05-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:48:39+00:00</t>
+    <t>2025-06-04T13:32:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -691,7 +691,7 @@
     <t>supportingInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {workflow-supportingInfo}
+    <t xml:space="preserve">Extension {workflow-supportingInfo|5.2.0}
 </t>
   </si>
   <si>
@@ -1718,7 +1718,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/hspc/ValueSet/respiratoryRateMeasMethodVS</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-respiratory-rate-meas-method</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -2454,7 +2454,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.03515625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T13:32:30+00:00</t>
+    <t>2025-06-24T17:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T17:01:22+00:00</t>
+    <t>2025-07-04T12:19:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T12:19:33+00:00</t>
+    <t>2025-07-08T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T13:28:39+00:00</t>
+    <t>2025-07-16T09:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T09:34:35+00:00</t>
+    <t>2025-07-30T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T14:55:53+00:00</t>
+    <t>2025-10-08T07:32:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -691,7 +691,7 @@
     <t>supportingInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {workflow-supportingInfo|5.2.0}
+    <t xml:space="preserve">Extension {workflow-supportingInfo|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -4970,7 +4970,7 @@
         <v>82</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>123</v>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:32:57+00:00</t>
+    <t>2025-10-08T12:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T12:04:30+00:00</t>
+    <t>2025-10-08T16:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:09:47+00:00</t>
+    <t>2026-03-25T10:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:11+00:00</t>
+    <t>2026-03-25T10:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:40+00:00</t>
+    <t>2026-03-25T10:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:25:13+00:00</t>
+    <t>2026-03-25T15:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:00:47+00:00</t>
+    <t>2026-03-31T09:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:16:18+00:00</t>
+    <t>2026-05-07T06:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:50:40+00:00</t>
+    <t>2026-05-27T14:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:53:55+00:00</t>
+    <t>2026-05-28T14:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:22:24+00:00</t>
+    <t>2026-06-12T14:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:04:24+00:00</t>
+    <t>2026-06-12T14:05:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:05:00+00:00</t>
+    <t>2026-06-12T14:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:35:23+00:00</t>
+    <t>2026-06-26T12:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:32:04+00:00</t>
+    <t>2026-06-29T09:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:30:52+00:00</t>
+    <t>2026-07-22T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:07+00:00</t>
+    <t>2026-07-27T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:02:31+00:00</t>
+    <t>2026-08-03T12:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:52:25+00:00</t>
+    <t>2026-08-04T12:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:22:31+00:00</t>
+    <t>2026-08-04T12:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-resp-rate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:29:23+00:00</t>
+    <t>2026-08-10T16:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
